--- a/output/graficos_dimensiones/comunal_e_matricula_a_2021_los_lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2021_los_lagos.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:24</t>
+    <t xml:space="preserve">2026-09-10 01:39</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2021_los_lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2021_los_lagos.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:39</t>
+    <t xml:space="preserve">2026-09-18 11:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2021_los_lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2021_los_lagos.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 11:35</t>
+    <t xml:space="preserve">2026-09-23 15:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2021_los_lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2021_los_lagos.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 15:40</t>
+    <t xml:space="preserve">2026-10-05 16:56</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
